--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Professionnel.</t>
+    <t>1.3.1- Professionnel / Structure</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Un professionnel (personne physique) via son logiciel de professionnel.</t>
+    <t>Un professionnel et/ou une structure ayant fourni des informations concernant le document (rôle d’informateur).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -247,40 +247,64 @@
     <t>Base</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.roleFonctionnel</t>
+    <t>ProfessionnelDocument.identifiant</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifiant de la personne.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.professionSavoirFaireRole</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Rôle fonctionnel de l’auteur.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.precisionRoleFonctionnel</t>
-  </si>
-  <si>
-    <t>Précision sur le rôle fonctionnel.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur</t>
+    <t>Profession / savoir-faire ou rôle.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.adresse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address
+</t>
+  </si>
+  <si>
+    <t>Adresse.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.coordonneesTelecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
+</t>
+  </si>
+  <si>
+    <t>Coordonnées télécom.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.personnePhysique</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Identification de l’auteur.</t>
+    <t>Personne physique.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.id</t>
+    <t>ProfessionnelDocument.personnePhysique.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -296,7 +320,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.extension</t>
+    <t>ProfessionnelDocument.personnePhysique.extension</t>
   </si>
   <si>
     <t>extensions
@@ -333,7 +357,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.modifierExtension</t>
+    <t>ProfessionnelDocument.personnePhysique.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -356,121 +380,85 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.identifiant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifiant de l’auteur.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.professionSavoirFaireRole</t>
-  </si>
-  <si>
-    <t>Profession / savoir-faire ou rôle.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.adresse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address
-</t>
-  </si>
-  <si>
-    <t>Adresse.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>Coordonnées télécom.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur</t>
-  </si>
-  <si>
-    <t>Identité de l’auteur.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.id</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.extension</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.modifierExtension</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur</t>
-  </si>
-  <si>
-    <t>Nom de l'auteur.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.id</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.extension</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.modifierExtension</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.nom</t>
-  </si>
-  <si>
-    <t>Nom de famille ou du nom d’usage.</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.prenom</t>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne</t>
+  </si>
+  <si>
+    <t>Identité de la personne physique.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.id</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.extension</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.modifierExtension</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.nomPersonne</t>
+  </si>
+  <si>
+    <t>Nom.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.prenomPersonne</t>
   </si>
   <si>
     <t>Prénom.</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.civilite</t>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.civilite</t>
   </si>
   <si>
     <t>Civilité.</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.identiteAuteur.nomAuteur.titre</t>
+    <t>ProfessionnelDocument.personnePhysique.identitePersonne.titre</t>
   </si>
   <si>
     <t>Titre.</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.structure</t>
+    <t>ProfessionnelDocument.structure</t>
   </si>
   <si>
     <t>Structure.</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.structure.id</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.structure.extension</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.structure.modifierExtension</t>
-  </si>
-  <si>
-    <t>ProfessionnelDocument.identificationAuteur.structure.identifiantStructure</t>
+    <t>ProfessionnelDocument.structure.id</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.structure.extension</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.structure.modifierExtension</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.structure.identifiantStructure</t>
   </si>
   <si>
     <t>Identifiant de la structure.</t>
   </si>
   <si>
-    <t>ProfessionnelDocument.identificationAuteur.structure.nomStructure</t>
+    <t>ProfessionnelDocument.structure.nomStructure</t>
   </si>
   <si>
     <t>Nom de la structure.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.structure.coordonneesTelecomStructure</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.structure.adresseStructure</t>
+  </si>
+  <si>
+    <t>Addresse.</t>
+  </si>
+  <si>
+    <t>ProfessionnelDocument.structure.cadreExercice</t>
+  </si>
+  <si>
+    <t>Cadre d'exercice.</t>
   </si>
 </sst>
 </file>
@@ -772,11 +760,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="83.37890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="83.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="73.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="73.5625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -806,7 +794,7 @@
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="73.87890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="72.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1035,7 +1023,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>78</v>
@@ -1110,7 +1098,7 @@
         <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>78</v>
@@ -1150,13 +1138,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1224,10 +1212,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1235,7 +1223,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>74</v>
@@ -1250,13 +1238,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1307,10 +1295,10 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>74</v>
@@ -1319,7 +1307,7 @@
         <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -1338,7 +1326,7 @@
         <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1356,7 +1344,7 @@
         <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1407,13 +1395,13 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>72</v>
@@ -1424,21 +1412,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1450,17 +1438,15 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>72</v>
@@ -1497,75 +1483,71 @@
         <v>72</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N8" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="O8" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>72</v>
       </c>
@@ -1613,31 +1595,31 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1656,15 +1638,17 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>72</v>
@@ -1701,19 +1685,19 @@
         <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1725,47 +1709,51 @@
         <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M10" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>72</v>
       </c>
@@ -1813,27 +1801,27 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1841,10 +1829,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -1856,13 +1844,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1913,27 +1901,27 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1944,7 +1932,7 @@
         <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
@@ -1956,13 +1944,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2013,13 +2001,13 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
@@ -2030,21 +2018,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2056,15 +2044,17 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
@@ -2101,71 +2091,75 @@
         <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>72</v>
       </c>
@@ -2213,38 +2207,38 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2256,17 +2250,15 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>72</v>
@@ -2303,75 +2295,71 @@
         <v>72</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>72</v>
       </c>
@@ -2419,19 +2407,19 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -2447,7 +2435,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>78</v>
@@ -2462,7 +2450,7 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>127</v>
@@ -2522,7 +2510,7 @@
         <v>126</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>78</v>
@@ -2531,7 +2519,7 @@
         <v>72</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -2562,13 +2550,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2619,7 +2607,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2636,21 +2624,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
@@ -2662,17 +2650,15 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>72</v>
@@ -2709,75 +2695,71 @@
         <v>72</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="O20" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>72</v>
       </c>
@@ -2825,38 +2807,38 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>72</v>
@@ -2868,15 +2850,17 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>72</v>
@@ -2913,71 +2897,75 @@
         <v>72</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>72</v>
       </c>
@@ -3025,19 +3013,19 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23">
@@ -3056,7 +3044,7 @@
         <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
@@ -3068,7 +3056,7 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>136</v>
@@ -3131,7 +3119,7 @@
         <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>72</v>
@@ -3168,7 +3156,7 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>138</v>
@@ -3253,10 +3241,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>72</v>
@@ -3268,13 +3256,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3328,24 +3316,24 @@
         <v>139</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3356,7 +3344,7 @@
         <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -3368,13 +3356,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3425,13 +3413,13 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>
@@ -3449,14 +3437,14 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>72</v>
@@ -3468,17 +3456,15 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>72</v>
@@ -3515,334 +3501,30 @@
         <v>72</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q28" s="2"/>
-      <c r="R28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-ProfessionnelDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
